--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -687,7 +687,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh dữ liệu có sẵn ở bước huấn luyện với dữ liệu thật sự có khi sinh tuần tự.</t>
+          <t>Khi dự đoán token ở vị trí 5, việc che token ở vị trí 6 (causal mask) là bắt buộc vì nếu cho phép nhìn thấy vị trí 6, mô hình sẽ bị rò rỉ thông tin tương lai - điều không thể xảy ra khi sinh văn bản tự hồi quy ở thời điểm suy luận.</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh từng chỉ số key với chỉ số query.</t>
+          <t>Trong decoder nhân quả, query tại vị trí 3 chỉ được phép chú ý tới các key tại vị trí &lt;= 3. Việc mask cho phép key 4 làm rò rỉ thông tin tương lai vào bước suy luận hiện tại.</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Residual nghĩa là giữ một đường đi tắt của biểu diễn trước tầng biến đổi.</t>
+          <t>Đường kết nối tắt residual (residual skip connection) quanh khối attention nhận đầu vào ban đầu `x` và cộng trực tiếp với đầu ra của tầng `Attention(x)`, tạo thành `x + Attention(x)` trước khi đi vào LayerNorm.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi biến nào phải được tạo trước khi xuất hiện ở vế phải.</t>
+          <t>Thứ tự qua khối Transformer (Post-Norm): attention tính a = Attention(x) (o2) -&gt; residual &amp; norm tính r1 = Norm(x + a) (o4) -&gt; feed-forward tính f = FFN(r1) (o1) -&gt; residual &amp; norm thứ hai tính r2 = Norm(r1 + f) (o3).</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chuỗi nguồn khỏi tiền tố token đích, rồi hỏi đường nào nối hai phía.</t>
+          <t>Self-attention của encoder (x1) truy cập các vị trí nguồn trong đầu vào encoder (r1); Causal self-attention của decoder (x2) truy cập các vị trí token đích hiện tại hoặc quá khứ (r2); Cross-attention của decoder (x3) truy cập đầu ra encoder khi decoder sinh token đích (r3).</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra có hai ngăn xếp nguồn/đích và cross-attention, hay chỉ một ngăn xếp nhân quả.</t>
+          <t>Mô hình nhận lời nhắc trong cùng một chuỗi và sinh token tiếp theo theo kiểu tự hồi quy mà không có encoder riêng hay cross-attention thuộc họ kiến trúc Transformer chỉ có decoder (Decoder-only Transformer, như GPT, LLaMA).</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu không chỉ có một câu trả lời đích; nó so sánh hai câu trả lời.</t>
+          <t>Tập dữ liệu gồm chỉ dẫn, hai câu trả lời A/B và nhãn người đánh giá thích A hơn B là dữ liệu so sánh ưu tiên trực tiếp phục vụ giai đoạn căn chỉnh theo ưu tiên (preference alignment, như RLHF hoặc DPO).</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt dữ liệu giám sát, mô hình chấm điểm và mô hình sinh câu trả lời.</t>
+          <t>Câu trả lời mẫu do con người viết (x1) là đích giám sát cho hành vi ban đầu (SFT target) (r1); Nhãn ưu tiên A hơn B (x2) là tín hiệu xếp hạng các câu trả lời (r2); Mô hình thưởng (x3) ước lượng điểm thưởng cho câu trả lời (r3); Mô hình chính sách policy (x4) là mô hình sinh câu trả lời được tối ưu (r4).</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm pipeline không có bước huấn luyện reward model riêng và vòng lặp tối ưu policy bằng RL.</t>
+          <t>Phương pháp tối ưu policy trực tiếp từ các cặp câu trả lời ưu tiên với một policy tham chiếu mà không cần huấn luyện reward model riêng hay chạy thuật toán RL là DPO (Direct Preference Optimization).</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng loại bỏ các cặp ưu tiên chỉ vì phương pháp này được gọi là trực tiếp.</t>
+          <t>DPO tối ưu trực tiếp policy từ dữ liệu ưu tiên thông qua hàm mất mát dạng phân loại nhị phân, do đó không cần giai đoạn huấn luyện reward model riêng (a) và không cần vòng lặp học tăng cường PPO (b).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -808,10 +808,15 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Layer nói về độ sâu; head nói về các góc nhìn attention bên trong layer.
-Phân tích theo nguyên lý thiết kế: Layer nói về độ sâu; head nói về các góc nhìn attention bên trong layer.</t>
+- Sửa phát biểu chính xác (1.5 điểm): Khẳng định 8 heads hoạt động song song trong 1 layer chứ không phải 8 layers nối tiếp.
+- Nêu rõ mục đích kỹ thuật (1.5 điểm): Giải thích việc cho phép mô hình đồng thời nắm bắt nhiều khía cạnh ngữ nghĩa/cú pháp khác nhau trong các không gian con.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Sửa phát biểu sai: Phát biểu trên không chính xác. '8 heads' (8 đầu chú ý) trong Multi-Head Attention đại diện cho 8 không gian con (subspaces) hoạt động SONG SONG (in parallel) cùng một lúc bên trong MỘT layer duy nhất, chứ không phải là 8 layers xử lý nối tiếp theo chiều sâu.
+- Mục đích của 8 heads: Cho phép mô hình đồng thời chú ý (jointly attend) đến các khía cạnh thông tin khác nhau ở các vị trí khác nhau trong cùng một thời điểm. Ví dụ: một head chuyên theo dõi quan hệ cú pháp chủ-vị, một head theo dõi thực thể, một head theo dõi dấu câu hoặc liên kết ngữ nghĩa cự ly dài. Sau đó kết quả của 8 heads được ghép nối (concatenate) và nhân qua ma trận chiếu $W^O$ để tạo ra biểu diễn phong phú, đa chiều.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tương tự như việc sử dụng nhiều bộ lọc (multiple feature maps/kernels) trong mạng tích chập CNN, Multi-Head Attention chiếu Q, K, V thành $h$ không gian con có số chiều thấp hơn ($d_k = d_{model} / h$) để học các mối quan hệ đa dạng mà không làm tăng tổng chi phí tính toán.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Vaswani, A., et al. (2017). Attention Is All You Need. Section 3.2.2 Multi-Head Attention. https://arxiv.org/abs/1706.03762</t>
         </is>
       </c>
     </row>
@@ -1090,10 +1095,20 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hình dung hai cấu trúc: hai ngăn xếp nối bằng cross-attention so với một chuỗi nhân quả duy nhất.
-Phân tích theo nguyên lý thiết kế: Hình dung hai cấu trúc: hai ngăn xếp nối bằng cross-attention so với một chuỗi nhân quả duy nhất.</t>
+- Luồng thông tin Encoder-Decoder (1.5 điểm): Nêu rõ thông tin nguồn đi qua khối Encoder và đi vào Decoder qua tầng Cross-Attention riêng biệt.
+- Luồng thông tin Decoder-only (1.5 điểm): Nêu rõ nguồn và đích nối chung trong một chuỗi, thông tin đi vào token mới qua Masked Causal Self-Attention.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+So sánh luồng thông tin và đường dẫn thông tin nguồn vào token đích mới:
+1. Kiến trúc Encoder–Decoder (ví dụ: T5, BART):
+- Luồng thông tin: Văn bản nguồn được xử lý trọn vẹn và hai chiều (bidirectional) bởi khối Encoder để tạo ra ma trận biểu diễn ngữ cảnh nguồn (memory).
+- Đường vào token đích: Thông tin nguồn đi vào token đích mới thông qua các tầng Cross-Attention (Encoder-Decoder Attention) nằm xen kẽ giữa Masked Self-Attention và FFN trong Decoder. Tại đây, Query đến từ Decoder và Key, Value đến từ đầu ra của Encoder.
+2. Kiến trúc Decoder-only (ví dụ: GPT-4, Llama):
+- Luồng thông tin: Không có khối Encoder và Cross-Attention riêng biệt. Cả chuỗi nguồn (prompt) và chuỗi đích (completion) được nối chung thành một chuỗi duy nhất.
+- Đường vào token đích: Thông tin nguồn đi vào token đích mới trực tiếp thông qua cơ chế Masked Causal Self-Attention. Token đích mới có thể nhìn ngược lại tất cả các token nguồn đứng trước nó theo ma trận tam giác nhân quả.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Sự khác biệt kiến trúc giữa Encoder-Decoder và Decoder-only phản ánh sự đánh đổi giữa hiệu quả biểu diễn hai chiều (bidirectional context trong translation) và sự tinh gọn, tối ưu bộ nhớ KV cache khi mở rộng quy mô sinh tự hồi quy (autoregressive scaling).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Raffel, C., et al. (2020). Exploring the Limits of Transfer Learning with a Unified Text-to-Text Transformer. JMLR. https://arxiv.org/abs/1910.10683; Brown, T., et al. (2020). Language Models are Few-Shot Learners.</t>
         </is>
       </c>
     </row>
@@ -1225,10 +1240,17 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một câu trả lời mẫu khác với nhãn cho biết người đánh giá thích câu trả lời nào hơn.
-Phân tích theo nguyên lý thiết kế: Một câu trả lời mẫu khác với nhãn cho biết người đánh giá thích câu trả lời nào hơn.</t>
+- Phân loại đúng giai đoạn (1.5 điểm): Xác định chính xác đây là Supervised Fine-Tuning (SFT / Instruction Tuning).
+- Giải thích vì sao chưa phải căn chỉnh ưu tiên (1.5 điểm): Nêu rõ thiếu dữ liệu so sánh sở thích (chosen vs rejected) và không sử dụng cơ chế reward/DPO để phạt phản hồi kém.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại giai đoạn huấn luyện: Đây là giai đoạn Căn chỉnh chỉ dẫn có giám sát (Supervised Fine-Tuning - SFT / Instruction Tuning).
+2. Vì sao đây chưa phải là căn chỉnh theo ưu tiên (Preference Alignment):
+- Bản chất của căn chỉnh theo ưu tiên (như RLHF, DPO, KTO) đòi hỏi dữ liệu phản ánh sự so sánh sở thích (pairwise preference data) gồm các cặp câu trả lời `[chosen, rejected]` đối với cùng một prompt, kèm mô hình phần thưởng (Reward Model) hoặc hàm mất mát tối ưu hóa preference.
+- Trong bối cảnh này, tập dữ liệu chỉ bao gồm các mẫu trình diễn chuẩn mực đơn lẻ (demonstration pairs) từ giảng viên mà không có nhãn chỉ ra câu trả lời nào bị từ chối hay xếp hạng ưu tiên. Quá trình huấn luyện chỉ đơn thuần là tối đa hóa xác suất hợp lý cực đại (cross-entropy next-token loss) chứ chưa hề có cơ chế phạt câu trả lời kém.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Quy trình huấn luyện LLM tiêu chuẩn bao gồm 3 pha: Pre-training (học tự giám sát không nhãn) -&gt; SFT (học làm theo chỉ dẫn từ dữ liệu mẫu chuẩn) -&gt; Preference Alignment (RLHF/DPO để học theo sở thích và chuẩn mực an toàn của con người). SFT dạy mô hình 'cách hành xử theo khuôn mẫu', trong khi Preference Alignment dạy mô hình 'cách chọn phương án tối ưu khi có nhiều câu trả lời hợp lệ'.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ouyang, L., et al. (2022). Training language models to follow instructions with human feedback. NeurIPS 2022. https://arxiv.org/abs/2203.02155; Rafailov, R., et al. (2024). Direct Preference Optimization (DPO).</t>
         </is>
       </c>
     </row>
